--- a/data/再保偿付能力2025Q4-0901.xlsx
+++ b/data/再保偿付能力2025Q4-0901.xlsx
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3.2004</v>
+        <v>3.200389</v>
       </c>
       <c r="D18" t="n">
-        <v>3.1975</v>
+        <v>3.197543</v>
       </c>
       <c r="E18" t="n">
-        <v>6770145.18</v>
+        <v>6770145.19</v>
       </c>
       <c r="F18" t="n">
-        <v>6761386.61</v>
+        <v>6761386.62</v>
       </c>
       <c r="G18" t="n">
         <v>14771781.86</v>

--- a/data/再保偿付能力2025Q4-0901.xlsx
+++ b/data/再保偿付能力2025Q4-0901.xlsx
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3.200389</v>
+        <v>3.2004</v>
       </c>
       <c r="D18" t="n">
-        <v>3.197543</v>
+        <v>3.1975</v>
       </c>
       <c r="E18" t="n">
         <v>6770145.19</v>
